--- a/monitor-zentao/code/sendmsgbug.xlsx
+++ b/monitor-zentao/code/sendmsgbug.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22470" windowHeight="12270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="已发送通知的Bug" sheetId="1" state="visible" r:id="rId1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -5479,7 +5479,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>42394-</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5634,7 +5634,6 @@
           <t>2026-04-28 15:39:26</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -5722,7 +5721,6 @@
           <t>2026-04-28 15:36:57</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -5810,7 +5808,6 @@
           <t>2026-04-28 15:35:44</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -5898,7 +5895,6 @@
           <t>2026-04-28 15:33:01</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -5918,27 +5914,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>42394--</t>
+          <t>42293</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EPM</t>
+          <t>Disk Copy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EPM20.2.0</t>
+          <t>DC7.2.0</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EPM20.2</t>
+          <t>网络克隆</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>关于断网情况下活动入口没有保持上一次状态问题</t>
+          <t>【网络克隆】关于PXE下，存在一个错误弹窗的问题</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5958,40 +5954,39 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-04-28 13:14:15</t>
+          <t>2026-04-08 10:18:31</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:51</t>
+          <t>2026-04-28 18:14:46</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>陈明</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:10</t>
+          <t>2026-04-28 18:13:53</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>bydesign</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6004,14 +5999,14 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>2026-04-28 16:04:05</t>
+          <t>2026-04-28 18:15:04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6026,12 +6021,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>EPM20.2</t>
+          <t>中文版</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>关于断网情况下活动入口没有保持上一次状态问题</t>
+          <t>kafan版本的产品名称和图标错误</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6051,22 +6046,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>敖瑞麟</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-04-28 13:14:15</t>
+          <t>2026-04-01 15:09:49</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>敖瑞麟</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:51</t>
+          <t>2026-04-29 13:21:00</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6076,15 +6071,14 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:10</t>
+          <t>2026-04-29 13:18:06</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>bydesign</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6097,7 +6091,192 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>2026-04-28 16:32:51</t>
+          <t>2026-04-29 13:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>42400</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>网络克隆</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>【网络克隆】关于系统克隆完成后，点击exit无任何响应的问题</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:41:23</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:49:15</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:47:58</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:50:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>42412</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EPM20.2.0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>关于AD Brand以外AD版本依然显示了活动条的问题</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:29:36</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:49:21</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:48:53</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2026-05-08 13:50:04</t>
         </is>
       </c>
     </row>

--- a/monitor-zentao/code/sendmsgbug.xlsx
+++ b/monitor-zentao/code/sendmsgbug.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -6263,7 +6263,6 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6277,6 +6276,564 @@
       <c r="S60" t="inlineStr">
         <is>
           <t>2026-05-08 13:50:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>42481</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>关于Discovery页本地ECG安装不成功问题</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:34:08</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:00:25</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:00:20</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>42435</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>关于EPM Clean页面，Space Analysis显示数据不会刷新的问题</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:33:39</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:15:36</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-05-15 15:38:38</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>nonproblem</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>42467</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>关于Clean-空间分析，没有屏蔽网络映射和exFAT的问题</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-15 10:05:28</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:14:24</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-05-15 10:46:06</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>bydesign</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>42470</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EPM20.5</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>关于同一路径Space Analyze扫描出来的数据是不一样的</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-15 10:56:10</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:10</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>谢蜀岷</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:19:41</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:10</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>42421</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>关于Clean页面，多次点击调用Space Analysis，会蓝屏的问题</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-09 11:05:19</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:14:11</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>谢蜀岷</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:13:33</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>42461</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>当ECG清理完成后点击关闭时，有可能导致系统崩溃</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>刘冬</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:15:59</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>邓贵星</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:15:04</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>谢蜀岷</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:05:21</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>notrepro</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:19:52</t>
         </is>
       </c>
     </row>

--- a/monitor-zentao/code/sendmsgbug.xlsx
+++ b/monitor-zentao/code/sendmsgbug.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -6355,7 +6355,6 @@
           <t>duplicate</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6448,7 +6447,6 @@
           <t>nonproblem</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6541,7 +6539,6 @@
           <t>bydesign</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6609,7 +6606,6 @@
           <t>2026-05-15 10:56:10</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>2026-05-19 17:22:10</t>
@@ -6727,7 +6723,6 @@
           <t>duplicate</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6820,7 +6815,6 @@
           <t>notrepro</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
@@ -6834,6 +6828,99 @@
       <c r="S66" t="inlineStr">
         <is>
           <t>2026-05-20 16:19:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>42483</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>关于clean页面调用出了本地ecg程序问题</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-05-21 08:55:22</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:55:55</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-05-21 10:53:50</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:00:06</t>
         </is>
       </c>
     </row>
